--- a/web/public/forms/orig/o-paengi-gyehoekseo.xlsx
+++ b/web/public/forms/orig/o-paengi-gyehoekseo.xlsx
@@ -1010,7 +1010,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="59" t="inlineStr">
@@ -2532,7 +2532,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
@@ -5080,7 +5080,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -5650,7 +5650,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -7062,7 +7062,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="59" t="inlineStr">
@@ -7159,7 +7159,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="59" t="inlineStr">
@@ -8956,7 +8956,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="L1" s="59" t="inlineStr">
@@ -9809,7 +9809,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="59" t="inlineStr">

--- a/web/public/forms/orig/o-paengi-gyehoekseo.xlsx
+++ b/web/public/forms/orig/o-paengi-gyehoekseo.xlsx
@@ -901,7 +901,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1000,7 +1000,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
@@ -3350,7 +3350,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -3921,7 +3921,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
